--- a/forms/trg/Formulir_TRG_aerodyn.xlsx
+++ b/forms/trg/Formulir_TRG_aerodyn.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Keahlian anggota banyak yang kosong. Mohon pilih keahlian utama untuk setiap anggota.</t>
+          <t>ID peneliti (SINTA/Scopus/ORCID) banyak yang kosong.</t>
         </is>
       </c>
     </row>
@@ -698,126 +698,114 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ID peneliti (SINTA/Scopus/ORCID) banyak yang kosong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
           <t>Belum ada artikel tercatat di situs. Mohon cantumkan riset terbaik di lembar TRG &amp; Riset.</t>
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Contoh pengisian (hanya ilustrasi, jangan disalin)</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Contoh pengisian (hanya ilustrasi, jangan disalin)</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Nama</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Dr. Contoh Nama, S.Pi., M.Si.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Nama</t>
+          <t>Keahlian utama 1-3 (pilih)</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Dr. Contoh Nama, S.Pi., M.Si.</t>
+          <t>Perikanan &amp; akuakultur; Ekosistem pesisir &amp; laut</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Keahlian utama 1-3 (pilih)</t>
+          <t>Kata kunci keahlian</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Perikanan &amp; akuakultur; Ekosistem pesisir &amp; laut</t>
+          <t>budidaya udang, kualitas air, bioflok</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Kata kunci keahlian</t>
+          <t>SINTA ID</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>budidaya udang, kualitas air, bioflok</t>
+          <t>6012345</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>SINTA ID</t>
+          <t>ORCID</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>6012345</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>ORCID</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
           <t>0000-0002-1234-5678</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Kemajuan pengisian (otomatis)</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Kemajuan pengisian (otomatis)</t>
-        </is>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Anggota tercantum</t>
+        </is>
+      </c>
+      <c r="B25" s="7">
+        <f>COUNTA(Anggota!B5:B27)</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Anggota tercantum</t>
+          <t>Anggota dengan keahlian terpilih</t>
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Anggota dengan keahlian terpilih</t>
-        </is>
-      </c>
-      <c r="B27" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
           <t>Persentase anggota berkeahlian</t>
         </is>
       </c>
-      <c r="B28" s="8">
-        <f>IF(B26=0,0,B27/B26)</f>
+      <c r="B27" s="8">
+        <f>IF(B25=0,0,B26/B25)</f>
         <v/>
       </c>
     </row>
@@ -832,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -937,29 +925,29 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Ir. Lukman Kasim, ST., MT.</t>
+          <t>Prof, Dr. Ir. Rustan Tarakka, ST., MT.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>University Hasanuddin</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Energy Conversion</t>
+          <t>Energy Conversion, Fluid Mechanics</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-6083-650X</t>
+        </is>
+      </c>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="12" t="n"/>
       <c r="M5" s="11" t="inlineStr">
@@ -974,12 +962,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr-Eng. Ir. Andi Amijoyo Mochtar, M.Sc.</t>
+          <t>Ir. Lukman Kasim, ST., MT.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1011,12 +999,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Nasaruddin Salam, MT.</t>
+          <t>Dr-Eng. Ir. Andi Amijoyo Mochtar, M.Sc.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1026,18 +1014,14 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Energy Conversion, Fluid Mechanics</t>
+          <t>Energy Conversion</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-4213-531X</t>
-        </is>
-      </c>
+      <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
@@ -1052,29 +1036,33 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Assoc. Prof. Ir. Dr. Shabuddin Bin Mat</t>
+          <t>Prof. Dr. Ir. Nasaruddin Salam, MT.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Universiti Teknologi Malaysia</t>
+          <t>University Hasanuddin</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Aerodynamic</t>
+          <t>Energy Conversion, Fluid Mechanics</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-4213-531X</t>
+        </is>
+      </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
@@ -1089,20 +1077,24 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Haslinah</t>
+          <t>Assoc. Prof. Ir. Dr. Shabuddin Bin Mat</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>University Hasanuddin</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="n"/>
+          <t>Universiti Teknologi Malaysia</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Aerodynamic</t>
+        </is>
+      </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
@@ -1122,12 +1114,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Nur Al Faqih Imam Jafar</t>
+          <t>Haslinah</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1140,11 +1132,7 @@
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>0009-0005-5699-2998</t>
-        </is>
-      </c>
+      <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
@@ -1159,12 +1147,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Alfathi Adam</t>
+          <t>Nur Al Faqih Imam Jafar</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1177,7 +1165,11 @@
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>0009-0005-5699-2998</t>
+        </is>
+      </c>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
@@ -1192,12 +1184,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Elieser Timbayo</t>
+          <t>Alfathi Adam</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1225,12 +1217,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Arief Dwi Yulianto AP</t>
+          <t>Elieser Timbayo</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1258,12 +1250,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Muh. Alfin Fauzhy</t>
+          <t>Arief Dwi Yulianto AP</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1289,10 +1281,26 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Muh. Alfin Fauzhy</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>University Hasanuddin</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>The Applied Aerodynamic Research Group is a research group that focuses on the study, development and application of aerodynamic principles in the land and air transportation sector. In the automotive and aviation industries, aerodynamic optimization plays a crucial role in reducing air resistance, improving fuel efficiency, and improving vehicle stability and safety. By utilizing experimental, computational, and theoretical analysis methods, it is hoped that it will be able to understand the phenomenon of airflow and develop innovative techniques in flow control and aerodynamic design to support a more efficient, fast, and environmentally friendly transportation system</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1300,7 +1308,11 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1489,15 +1501,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
